--- a/data/240716_exp_gas_consumption.xlsx
+++ b/data/240716_exp_gas_consumption.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adam-1y9pxi6q95ggpmx\Documents\PhD\10-19 Research\11 Data\11.03 Fluxes values\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adam-1y9pxi6q95ggpmx\Documents\PhD\SoF1-GEM\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285D71D1-DB4D-4A1A-B70A-1DF01C8800B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1616D8A2-8BC5-4DD4-B23F-A041B8D41B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,12 +26,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Group name </t>
   </si>
@@ -96,24 +99,6 @@
     <t>CO2 flux theoretic</t>
   </si>
   <si>
-    <t>H2 Flux model</t>
-  </si>
-  <si>
-    <t>O2 Flux model</t>
-  </si>
-  <si>
-    <t>CO2 Flux model</t>
-  </si>
-  <si>
-    <t>H2/CO2.1</t>
-  </si>
-  <si>
-    <t>O2/CO2.1</t>
-  </si>
-  <si>
-    <t>H2/O2.1</t>
-  </si>
-  <si>
     <t>SF72-107 </t>
   </si>
   <si>
@@ -183,16 +168,7 @@
     <t>D6</t>
   </si>
   <si>
-    <t>model_growth_rate</t>
-  </si>
-  <si>
-    <t>exp_dilRate</t>
-  </si>
-  <si>
-    <t>Flux theoretic is the theoretic conversion from  gas consumption to standard flux that can be used as a constraint in the model.</t>
-  </si>
-  <si>
-    <t>Model flux are how much uptake flux the model have from the theoretic flux</t>
+    <t>exp_growth</t>
   </si>
 </sst>
 </file>
@@ -202,7 +178,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,11 +194,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -271,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -281,12 +252,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -595,37 +560,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:V18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.54296875" customWidth="1"/>
-    <col min="3" max="3" width="20.08984375" customWidth="1"/>
-    <col min="4" max="4" width="19.90625" customWidth="1"/>
-    <col min="5" max="5" width="17.90625" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" customWidth="1"/>
-    <col min="9" max="9" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="21.1796875" customWidth="1"/>
-    <col min="12" max="12" width="24.54296875" customWidth="1"/>
-    <col min="13" max="13" width="14.7265625" customWidth="1"/>
-    <col min="14" max="14" width="18.6328125" customWidth="1"/>
-    <col min="15" max="15" width="15.26953125" customWidth="1"/>
-    <col min="16" max="16" width="12.26953125" customWidth="1"/>
-    <col min="17" max="17" width="12.6328125" customWidth="1"/>
-    <col min="18" max="18" width="9.54296875" customWidth="1"/>
-    <col min="19" max="19" width="20.26953125" customWidth="1"/>
-    <col min="20" max="20" width="15.453125" customWidth="1"/>
-    <col min="21" max="21" width="18.453125" customWidth="1"/>
-    <col min="22" max="22" width="16.6328125" customWidth="1"/>
-    <col min="23" max="23" width="17.08984375" customWidth="1"/>
-    <col min="24" max="24" width="15.81640625" customWidth="1"/>
-    <col min="25" max="25" width="12.453125" customWidth="1"/>
-    <col min="28" max="28" width="12.54296875" customWidth="1"/>
-    <col min="29" max="29" width="11.81640625" customWidth="1"/>
+    <col min="11" max="11" width="21.140625" customWidth="1"/>
+    <col min="12" max="12" width="24.5703125" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="14" max="14" width="18.5703125" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" customWidth="1"/>
+    <col min="16" max="16" width="12.28515625" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" customWidth="1"/>
+    <col min="19" max="19" width="20.28515625" customWidth="1"/>
+    <col min="20" max="20" width="15.42578125" customWidth="1"/>
+    <col min="21" max="21" width="18.42578125" customWidth="1"/>
+    <col min="22" max="22" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,36 +650,15 @@
         <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>44</v>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C2" s="4">
         <v>2.1801089049180327</v>
@@ -786,37 +725,13 @@
         <v>2.5132229840684461</v>
       </c>
       <c r="V2" s="4">
-        <v>-16.77</v>
-      </c>
-      <c r="W2" s="4">
-        <v>-5.89</v>
-      </c>
-      <c r="X2" s="4">
-        <v>-2.5</v>
-      </c>
-      <c r="Y2" s="4">
-        <f>V2/X2</f>
-        <v>6.7080000000000002</v>
-      </c>
-      <c r="Z2" s="4">
-        <f>W2/X2</f>
-        <v>2.3559999999999999</v>
-      </c>
-      <c r="AA2" s="4">
-        <f>V2/W2</f>
-        <v>2.8471986417657047</v>
-      </c>
-      <c r="AB2" s="5">
-        <v>6.3E-2</v>
-      </c>
-      <c r="AC2" s="4">
         <v>4.6333164894716068E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="5"/>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C3" s="4">
         <v>2.180122324590164</v>
@@ -876,37 +791,13 @@
         <v>2.4599688825211228</v>
       </c>
       <c r="V3" s="4">
-        <v>-18.52371060495101</v>
-      </c>
-      <c r="W3" s="4">
-        <v>-6.8119749205242881</v>
-      </c>
-      <c r="X3" s="4">
-        <v>-2.4599688825211228</v>
-      </c>
-      <c r="Y3" s="4">
-        <f t="shared" ref="Y3:Y18" si="1">V3/X3</f>
-        <v>7.5300589111382603</v>
-      </c>
-      <c r="Z3" s="4">
-        <f t="shared" ref="Z3:Z18" si="2">W3/X3</f>
-        <v>2.769130523936941</v>
-      </c>
-      <c r="AA3" s="4">
-        <f t="shared" ref="AA3:AA18" si="3">V3/W3</f>
-        <v>2.7192863774556177</v>
-      </c>
-      <c r="AB3" s="6">
-        <v>5.9954867123860729E-2</v>
-      </c>
-      <c r="AC3" s="4">
         <v>4.603843657912355E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A4" s="7"/>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4">
         <v>2.1801200409836068</v>
@@ -966,39 +857,15 @@
         <v>2.5554313237156081</v>
       </c>
       <c r="V4" s="4">
-        <v>-19.241162748347119</v>
-      </c>
-      <c r="W4" s="4">
-        <v>-7.0756300490258068</v>
-      </c>
-      <c r="X4" s="4">
-        <v>-2.5554313237156081</v>
-      </c>
-      <c r="Y4" s="4">
-        <f t="shared" si="1"/>
-        <v>7.529516668978756</v>
-      </c>
-      <c r="Z4" s="4">
-        <f t="shared" si="2"/>
-        <v>2.7688594028572093</v>
-      </c>
-      <c r="AA4" s="4">
-        <f t="shared" si="3"/>
-        <v>2.7193568085143593</v>
-      </c>
-      <c r="AB4" s="6">
-        <v>6.2281497358003438E-2</v>
-      </c>
-      <c r="AC4" s="4">
         <v>4.6109320258048342E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
-        <v>45</v>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C5" s="4">
         <v>2.0801136426229512</v>
@@ -1058,37 +925,13 @@
         <v>2.057798143618951</v>
       </c>
       <c r="V5" s="4">
-        <v>-16.73683317676619</v>
-      </c>
-      <c r="W5" s="4">
-        <v>-6.3190576156383136</v>
-      </c>
-      <c r="X5" s="4">
-        <v>-2.057798143618951</v>
-      </c>
-      <c r="Y5" s="4">
-        <f t="shared" si="1"/>
-        <v>8.1333697518707666</v>
-      </c>
-      <c r="Z5" s="4">
-        <f t="shared" si="2"/>
-        <v>3.0707859443032102</v>
-      </c>
-      <c r="AA5" s="4">
-        <f t="shared" si="3"/>
-        <v>2.6486280383559273</v>
-      </c>
-      <c r="AB5" s="6">
-        <v>5.015307922999189E-2</v>
-      </c>
-      <c r="AC5" s="4">
         <v>3.3814142804236128E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A6" s="7"/>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C6" s="4">
         <v>2.0801316704918031</v>
@@ -1148,37 +991,13 @@
         <v>2.0681594979546301</v>
       </c>
       <c r="V6" s="4">
-        <v>-16.816460350045521</v>
-      </c>
-      <c r="W6" s="4">
-        <v>-6.348552340564777</v>
-      </c>
-      <c r="X6" s="4">
-        <v>-2.0681594979546301</v>
-      </c>
-      <c r="Y6" s="4">
-        <f t="shared" si="1"/>
-        <v>8.1311235263415007</v>
-      </c>
-      <c r="Z6" s="4">
-        <f t="shared" si="2"/>
-        <v>3.0696628315385603</v>
-      </c>
-      <c r="AA6" s="4">
-        <f t="shared" si="3"/>
-        <v>2.6488653551133048</v>
-      </c>
-      <c r="AB6" s="6">
-        <v>5.040560828710218E-2</v>
-      </c>
-      <c r="AC6" s="4">
         <v>3.5983292116139792E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A7" s="7"/>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4">
         <v>2.0801119655737712</v>
@@ -1238,39 +1057,15 @@
         <v>2.0494265289251401</v>
       </c>
       <c r="V7" s="4">
-        <v>-16.638264150182469</v>
-      </c>
-      <c r="W7" s="4">
-        <v>-6.2781103844760198</v>
-      </c>
-      <c r="X7" s="4">
-        <v>-2.0494265289251401</v>
-      </c>
-      <c r="Y7" s="4">
-        <f t="shared" si="1"/>
-        <v>8.1184974993510579</v>
-      </c>
-      <c r="Z7" s="4">
-        <f t="shared" si="2"/>
-        <v>3.0633498180433389</v>
-      </c>
-      <c r="AA7" s="4">
-        <f t="shared" si="3"/>
-        <v>2.6502025500099777</v>
-      </c>
-      <c r="AB7" s="6">
-        <v>4.9949044516324953E-2</v>
-      </c>
-      <c r="AC7" s="4">
         <v>3.5983292116139792E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
-        <v>46</v>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C8" s="4">
         <v>1.990138191803279</v>
@@ -1330,37 +1125,13 @@
         <v>1.5934304907922341</v>
       </c>
       <c r="V8" s="4">
-        <v>-14.82462278381405</v>
-      </c>
-      <c r="W8" s="4">
-        <v>-5.8254156684968814</v>
-      </c>
-      <c r="X8" s="4">
-        <v>-1.5934304907922341</v>
-      </c>
-      <c r="Y8" s="4">
-        <f t="shared" si="1"/>
-        <v>9.3035892494083186</v>
-      </c>
-      <c r="Z8" s="4">
-        <f t="shared" si="2"/>
-        <v>3.6558956930719684</v>
-      </c>
-      <c r="AA8" s="4">
-        <f t="shared" si="3"/>
-        <v>2.5448180228552193</v>
-      </c>
-      <c r="AB8" s="6">
-        <v>3.8835415368607247E-2</v>
-      </c>
-      <c r="AC8" s="4">
         <v>2.6490651372405961E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A9" s="7"/>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C9" s="4">
         <v>1.9901266540983611</v>
@@ -1420,37 +1191,13 @@
         <v>1.6083217797927669</v>
       </c>
       <c r="V9" s="4">
-        <v>-14.976211344733921</v>
-      </c>
-      <c r="W9" s="4">
-        <v>-5.8863797301505603</v>
-      </c>
-      <c r="X9" s="4">
-        <v>-1.6083217797927669</v>
-      </c>
-      <c r="Y9" s="4">
-        <f t="shared" si="1"/>
-        <v>9.3117008877810594</v>
-      </c>
-      <c r="Z9" s="4">
-        <f t="shared" si="2"/>
-        <v>3.6599515122583388</v>
-      </c>
-      <c r="AA9" s="4">
-        <f t="shared" si="3"/>
-        <v>2.5442142762255782</v>
-      </c>
-      <c r="AB9" s="6">
-        <v>3.9198348924260613E-2</v>
-      </c>
-      <c r="AC9" s="4">
         <v>2.6290537041244181E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A10" s="7"/>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C10" s="4">
         <v>1.990107537704918</v>
@@ -1510,39 +1257,15 @@
         <v>1.649321812470141</v>
       </c>
       <c r="V10" s="4">
-        <v>-15.247676048802409</v>
-      </c>
-      <c r="W10" s="4">
-        <v>-5.9812801934445217</v>
-      </c>
-      <c r="X10" s="4">
-        <v>-1.649321812470141</v>
-      </c>
-      <c r="Y10" s="4">
-        <f t="shared" si="1"/>
-        <v>9.244815616648161</v>
-      </c>
-      <c r="Z10" s="4">
-        <f t="shared" si="2"/>
-        <v>3.6265088766918891</v>
-      </c>
-      <c r="AA10" s="4">
-        <f t="shared" si="3"/>
-        <v>2.5492328658192354</v>
-      </c>
-      <c r="AB10" s="6">
-        <v>4.0197610146104457E-2</v>
-      </c>
-      <c r="AC10" s="4">
         <v>2.6290537041244181E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
-        <v>47</v>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C11" s="4">
         <v>1.890098670491803</v>
@@ -1602,37 +1325,13 @@
         <v>1.434691188178373</v>
       </c>
       <c r="V11" s="4">
-        <v>-15.08677963267921</v>
-      </c>
-      <c r="W11" s="4">
-        <v>-6.1145823948106459</v>
-      </c>
-      <c r="X11" s="4">
-        <v>-1.434691188178373</v>
-      </c>
-      <c r="Y11" s="4">
-        <f t="shared" si="1"/>
-        <v>10.51569826105567</v>
-      </c>
-      <c r="Z11" s="4">
-        <f t="shared" si="2"/>
-        <v>4.2619501988956445</v>
-      </c>
-      <c r="AA11" s="4">
-        <f t="shared" si="3"/>
-        <v>2.4673442368661402</v>
-      </c>
-      <c r="AB11" s="6">
-        <v>3.4966588464669157E-2</v>
-      </c>
-      <c r="AC11" s="4">
         <v>2.0828216038825471E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A12" s="7"/>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C12" s="4">
         <v>1.890124742622951</v>
@@ -1692,37 +1391,13 @@
         <v>1.3764704371337551</v>
       </c>
       <c r="V12" s="4">
-        <v>-14.53158387792708</v>
-      </c>
-      <c r="W12" s="4">
-        <v>-5.8949665011987404</v>
-      </c>
-      <c r="X12" s="4">
-        <v>-1.3764704371337551</v>
-      </c>
-      <c r="Y12" s="4">
-        <f t="shared" si="1"/>
-        <v>10.5571347454337</v>
-      </c>
-      <c r="Z12" s="4">
-        <f t="shared" si="2"/>
-        <v>4.2826684410846605</v>
-      </c>
-      <c r="AA12" s="4">
-        <f t="shared" si="3"/>
-        <v>2.4650833681535058</v>
-      </c>
-      <c r="AB12" s="6">
-        <v>3.3547620355953031E-2</v>
-      </c>
-      <c r="AC12" s="4">
         <v>2.11696284081858E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A13" s="7"/>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C13" s="4">
         <v>1.8901075491803281</v>
@@ -1782,39 +1457,15 @@
         <v>1.4829447400707749</v>
       </c>
       <c r="V13" s="4">
-        <v>-15.1765708258815</v>
-      </c>
-      <c r="W13" s="4">
-        <v>-6.1114223306346913</v>
-      </c>
-      <c r="X13" s="4">
-        <v>-1.4829447400707749</v>
-      </c>
-      <c r="Y13" s="4">
-        <f t="shared" si="1"/>
-        <v>10.234077114132509</v>
-      </c>
-      <c r="Z13" s="4">
-        <f t="shared" si="2"/>
-        <v>4.1211396254340658</v>
-      </c>
-      <c r="AA13" s="4">
-        <f t="shared" si="3"/>
-        <v>2.483312395185977</v>
-      </c>
-      <c r="AB13" s="6">
-        <v>3.6142633947406397E-2</v>
-      </c>
-      <c r="AC13" s="4">
         <v>2.017461580733303E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
-        <v>48</v>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C14" s="4">
         <v>1.9001156819672129</v>
@@ -1874,37 +1525,13 @@
         <v>1.690115875626869</v>
       </c>
       <c r="V14" s="4">
-        <v>-19.138350825094431</v>
-      </c>
-      <c r="W14" s="4">
-        <v>-7.8859908176758156</v>
-      </c>
-      <c r="X14" s="4">
-        <v>-1.690115875626869</v>
-      </c>
-      <c r="Y14" s="4">
-        <f t="shared" si="1"/>
-        <v>11.323691529727782</v>
-      </c>
-      <c r="Z14" s="4">
-        <f t="shared" si="2"/>
-        <v>4.6659468332317022</v>
-      </c>
-      <c r="AA14" s="4">
-        <f t="shared" si="3"/>
-        <v>2.426879674041384</v>
-      </c>
-      <c r="AB14" s="6">
-        <v>4.1191851436464699E-2</v>
-      </c>
-      <c r="AC14" s="4">
         <v>2.1498892456792301E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A15" s="7"/>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C15" s="4">
         <v>1.900109978688524</v>
@@ -1964,37 +1591,13 @@
         <v>1.554243314531691</v>
       </c>
       <c r="V15" s="4">
-        <v>-17.674486957357601</v>
-      </c>
-      <c r="W15" s="4">
-        <v>-7.2893742222402134</v>
-      </c>
-      <c r="X15" s="4">
-        <v>-1.554243314531691</v>
-      </c>
-      <c r="Y15" s="4">
-        <f t="shared" si="1"/>
-        <v>11.371763218864546</v>
-      </c>
-      <c r="Z15" s="4">
-        <f t="shared" si="2"/>
-        <v>4.6899826778000806</v>
-      </c>
-      <c r="AA15" s="4">
-        <f t="shared" si="3"/>
-        <v>2.4246919445337207</v>
-      </c>
-      <c r="AB15" s="6">
-        <v>3.7880337455893018E-2</v>
-      </c>
-      <c r="AC15" s="4">
         <v>2.1498892456792301E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A16" s="7"/>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C16" s="4">
         <v>1.900124232786885</v>
@@ -2054,39 +1657,15 @@
         <v>1.747703035744069</v>
       </c>
       <c r="V16" s="4">
-        <v>-19.428711723228979</v>
-      </c>
-      <c r="W16" s="4">
-        <v>-7.973820275506637</v>
-      </c>
-      <c r="X16" s="4">
-        <v>-1.747703035744069</v>
-      </c>
-      <c r="Y16" s="4">
-        <f t="shared" si="1"/>
-        <v>11.116712236502684</v>
-      </c>
-      <c r="Z16" s="4">
-        <f t="shared" si="2"/>
-        <v>4.5624571866191523</v>
-      </c>
-      <c r="AA16" s="4">
-        <f t="shared" si="3"/>
-        <v>2.4365625323796913</v>
-      </c>
-      <c r="AB16" s="6">
-        <v>4.2595377536896087E-2</v>
-      </c>
-      <c r="AC16" s="4">
         <v>2.1498892456792301E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
-        <v>49</v>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C17" s="4">
         <v>1.9001268442622949</v>
@@ -2146,37 +1725,13 @@
         <v>1.3984873466255121</v>
       </c>
       <c r="V17" s="4">
-        <v>-17.443296436218521</v>
-      </c>
-      <c r="W17" s="4">
-        <v>-7.3288961637037753</v>
-      </c>
-      <c r="X17" s="4">
-        <v>-1.3984873466255121</v>
-      </c>
-      <c r="Y17" s="4">
-        <f t="shared" si="1"/>
-        <v>12.472974087544246</v>
-      </c>
-      <c r="Z17" s="4">
-        <f t="shared" si="2"/>
-        <v>5.2405881121399318</v>
-      </c>
-      <c r="AA17" s="4">
-        <f t="shared" si="3"/>
-        <v>2.3800714386712323</v>
-      </c>
-      <c r="AB17" s="6">
-        <v>3.40842209985203E-2</v>
-      </c>
-      <c r="AC17" s="4">
         <v>1.8696884574294421E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A18" s="7"/>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C18" s="4">
         <v>1.900136665573771</v>
@@ -2236,41 +1791,7 @@
         <v>1.531555197291872</v>
       </c>
       <c r="V18" s="4">
-        <v>-17.76713694016345</v>
-      </c>
-      <c r="W18" s="4">
-        <v>-7.3582942853630247</v>
-      </c>
-      <c r="X18" s="4">
-        <v>-1.531555197291872</v>
-      </c>
-      <c r="Y18" s="4">
-        <f t="shared" si="1"/>
-        <v>11.600716037906876</v>
-      </c>
-      <c r="Z18" s="4">
-        <f t="shared" si="2"/>
-        <v>4.8044590873212503</v>
-      </c>
-      <c r="AA18" s="4">
-        <f t="shared" si="3"/>
-        <v>2.4145727598181947</v>
-      </c>
-      <c r="AB18" s="6">
-        <v>3.7327378000158069E-2</v>
-      </c>
-      <c r="AC18" s="4">
         <v>1.8367113320993809E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="S21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="S22" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
